--- a/data/trans_orig/P1802_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1802_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47892</t>
+          <t>47667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76149</t>
+          <t>76580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59445</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89351</t>
+          <t>89249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114672</t>
+          <t>112621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154479</t>
+          <t>154525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217612</t>
+          <t>217181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245869</t>
+          <t>246094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199352</t>
+          <t>199454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229258</t>
+          <t>228605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427985</t>
+          <t>427939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>467792</t>
+          <t>469843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95269</t>
+          <t>95181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85364</t>
+          <t>83754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122949</t>
+          <t>121816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154817</t>
+          <t>155166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205499</t>
+          <t>205865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407306</t>
+          <t>407394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438936</t>
+          <t>440222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400135</t>
+          <t>401268</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>437720</t>
+          <t>439330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820160</t>
+          <t>819794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>870842</t>
+          <t>870493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>47803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>42989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>73863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284495</t>
+          <t>285111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301834</t>
+          <t>302955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289317</t>
+          <t>288506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312288</t>
+          <t>312333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>581829</t>
+          <t>581011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>610742</t>
+          <t>611885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55254</t>
+          <t>54751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>86078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69899</t>
+          <t>69039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105286</t>
+          <t>102134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133257</t>
+          <t>134349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181656</t>
+          <t>179050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>283886</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314710</t>
+          <t>315213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281997</t>
+          <t>285149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>317384</t>
+          <t>318244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>575591</t>
+          <t>578197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>623990</t>
+          <t>622898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28315</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51271</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>64765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97134</t>
+          <t>97641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159950</t>
+          <t>159822</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182906</t>
+          <t>182469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>166691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187803</t>
+          <t>188773</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332674</t>
+          <t>332167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365340</t>
+          <t>365043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48794</t>
+          <t>47151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43922</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72094</t>
+          <t>70066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75300</t>
+          <t>75335</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110646</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214329</t>
+          <t>215972</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237961</t>
+          <t>237905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201021</t>
+          <t>203049</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229193</t>
+          <t>228690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425592</t>
+          <t>425734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>460938</t>
+          <t>460903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52414</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95065</t>
+          <t>95990</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137352</t>
+          <t>138061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156233</t>
+          <t>158183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207313</t>
+          <t>210775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>571278</t>
+          <t>571153</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604144</t>
+          <t>604032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>553942</t>
+          <t>553233</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596229</t>
+          <t>595304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1140539</t>
+          <t>1137077</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1191619</t>
+          <t>1189669</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94210</t>
+          <t>94567</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133759</t>
+          <t>132443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>144102</t>
+          <t>142087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192777</t>
+          <t>187639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248619</t>
+          <t>243270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>309957</t>
+          <t>307019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>644824</t>
+          <t>646140</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>684373</t>
+          <t>684016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>633390</t>
+          <t>638528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>682065</t>
+          <t>684080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1294793</t>
+          <t>1297731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1356131</t>
+          <t>1361480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>450601</t>
+          <t>447787</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>532950</t>
+          <t>530340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>623660</t>
+          <t>621069</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>717621</t>
+          <t>719257</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1094059</t>
+          <t>1093456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1227221</t>
+          <t>1223456</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2861400</t>
+          <t>2864010</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2943749</t>
+          <t>2946563</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2826921</t>
+          <t>2825285</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2920882</t>
+          <t>2923473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5711671</t>
+          <t>5715436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5844833</t>
+          <t>5845436</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>88891</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78311</t>
+          <t>72670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114456</t>
+          <t>104559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>113900</t>
+          <t>119109</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100883</t>
+          <t>105590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128147</t>
+          <t>131767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>208158</t>
+          <t>208000</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186174</t>
+          <t>189062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232187</t>
+          <t>230801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>217184</t>
+          <t>229954</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196987</t>
+          <t>214286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233132</t>
+          <t>246175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>175735</t>
+          <t>196952</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>161488</t>
+          <t>184294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188752</t>
+          <t>210471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>392919</t>
+          <t>426906</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>368890</t>
+          <t>404105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414903</t>
+          <t>445844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>70,22%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>58143</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40058</t>
+          <t>44312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71769</t>
+          <t>76372</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73418</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103758</t>
+          <t>109351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>143675</t>
+          <t>150745</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122376</t>
+          <t>129029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166285</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>463363</t>
+          <t>472504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446621</t>
+          <t>454275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478332</t>
+          <t>486335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>423671</t>
+          <t>451205</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408561</t>
+          <t>434456</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>438901</t>
+          <t>466008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>887034</t>
+          <t>923709</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>864424</t>
+          <t>899772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908333</t>
+          <t>945425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512319</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512319</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512319</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030709</t>
+          <t>1074454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030709</t>
+          <t>1074454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030709</t>
+          <t>1074454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70198</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>57384</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85599</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91548</t>
+          <t>93625</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79559</t>
+          <t>80441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106211</t>
+          <t>109032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>161746</t>
+          <t>164036</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140802</t>
+          <t>146890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181552</t>
+          <t>184952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>245852</t>
+          <t>245582</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>230451</t>
+          <t>231333</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258342</t>
+          <t>258609</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>257580</t>
+          <t>262756</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242917</t>
+          <t>247349</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269569</t>
+          <t>275940</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>503432</t>
+          <t>508339</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>483626</t>
+          <t>487423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>524376</t>
+          <t>525485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,15%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51470</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37211</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68611</t>
+          <t>72593</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>60671</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70995</t>
+          <t>74253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>105290</t>
+          <t>114142</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75368</t>
+          <t>94240</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130849</t>
+          <t>135489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>261087</t>
+          <t>319674</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243946</t>
+          <t>300552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>275346</t>
+          <t>334687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>421898</t>
+          <t>361290</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404723</t>
+          <t>347708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>443570</t>
+          <t>372797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>682984</t>
+          <t>680965</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>657425</t>
+          <t>659618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>712906</t>
+          <t>700867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31642</t>
+          <t>34094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>12588</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>36748</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27045</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>48582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>155647</t>
+          <t>181505</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147100</t>
+          <t>171571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163015</t>
+          <t>189072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>196987</t>
+          <t>214627</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192378</t>
+          <t>209438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200357</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>352634</t>
+          <t>396131</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341792</t>
+          <t>384297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>360353</t>
+          <t>404057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>56527</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51008</t>
+          <t>52030</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42213</t>
+          <t>42395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61169</t>
+          <t>62536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>97772</t>
+          <t>97729</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84047</t>
+          <t>81961</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114074</t>
+          <t>112648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>222872</t>
+          <t>225008</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209813</t>
+          <t>214180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232485</t>
+          <t>235069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>206048</t>
+          <t>211720</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195887</t>
+          <t>201214</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214843</t>
+          <t>221355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>428920</t>
+          <t>436728</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>412618</t>
+          <t>421809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442645</t>
+          <t>452496</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>128316</t>
+          <t>144544</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107456</t>
+          <t>121026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151715</t>
+          <t>168701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>167011</t>
+          <t>207813</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83654</t>
+          <t>186039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227823</t>
+          <t>231832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>295328</t>
+          <t>352357</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>182562</t>
+          <t>317610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>352575</t>
+          <t>383582</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>494504</t>
+          <t>573472</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>471105</t>
+          <t>549315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>515364</t>
+          <t>596990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>564244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621442</t>
+          <t>540225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>765611</t>
+          <t>586018</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1176756</t>
+          <t>1137716</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1119509</t>
+          <t>1106491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1289522</t>
+          <t>1172463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622820</t>
+          <t>718016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622820</t>
+          <t>718016</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622820</t>
+          <t>718016</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472084</t>
+          <t>1490073</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472084</t>
+          <t>1490073</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472084</t>
+          <t>1490073</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>287283</t>
+          <t>48714</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52479</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>635704</t>
+          <t>64639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>51165</t>
+          <t>61294</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>49471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63819</t>
+          <t>75074</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>338448</t>
+          <t>110009</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104712</t>
+          <t>91490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>830764</t>
+          <t>129999</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>641437</t>
+          <t>749358</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>293016</t>
+          <t>733433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>876241</t>
+          <t>761271</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>666016</t>
+          <t>769404</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>653362</t>
+          <t>755624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>675763</t>
+          <t>781227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1307453</t>
+          <t>1518761</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>815137</t>
+          <t>1498771</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1541189</t>
+          <t>1537280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717181</t>
+          <t>830698</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717181</t>
+          <t>830698</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717181</t>
+          <t>830698</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645901</t>
+          <t>1628770</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645901</t>
+          <t>1628770</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645901</t>
+          <t>1628770</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>535648</t>
+          <t>492282</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1357470</t>
+          <t>581716</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>519238</t>
+          <t>660448</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>689500</t>
+          <t>745858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1146383</t>
+          <t>1170974</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2120306</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2701945</t>
+          <t>2997057</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2100887</t>
+          <t>2949375</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2922709</t>
+          <t>3038809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3030187</t>
+          <t>3032198</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2969456</t>
+          <t>2986073</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3139718</t>
+          <t>3071483</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5732132</t>
+          <t>6029256</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4997007</t>
+          <t>5972558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5970930</t>
+          <t>6092048</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
